--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/mar-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/mar-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M302"/>
+  <dimension ref="A1:M301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>23000001.02</v>
+        <v>25277.69</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>24599300.15</v>
+        <v>27035.37</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2660000.93</v>
+        <v>2923.42</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>31374018.11</v>
+        <v>34480.99</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>68999999.67</v>
+        <v>75833.08</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>12728860.23</v>
+        <v>13989.4</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>24314400</v>
+        <v>26722.26</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>24179779.52</v>
+        <v>26574.31</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>71249999.91</v>
+        <v>78305.89</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1799999.52</v>
+        <v>1978.25</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>296400.14</v>
+        <v>325.75</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3520440</v>
+        <v>3869.07</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8174274.7</v>
+        <v>8983.77</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7557250.06</v>
+        <v>8305.65</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>28499999.96</v>
+        <v>31322.36</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2531759.27</v>
+        <v>2782.48</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6046239.58</v>
+        <v>6645</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1725000.64</v>
+        <v>1895.83</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1610000.44</v>
+        <v>1769.44</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1499999.4</v>
+        <v>1648.54</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>17600</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>555750.41</v>
+        <v>610.79</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9371991.199999999</v>
+        <v>10300.1</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>974700.14</v>
+        <v>1071.22</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5289399.23</v>
+        <v>5813.21</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2000000.33</v>
+        <v>2198.06</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>193800.48</v>
+        <v>212.99</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1130500</v>
+        <v>1242.45</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2507999.55</v>
+        <v>2756.37</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4759691.02</v>
+        <v>5231.04</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>12000031.4</v>
+        <v>13188.4</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1499999.4</v>
+        <v>1648.54</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5999999.87</v>
+        <v>6594.18</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>26547750.82</v>
+        <v>29176.78</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4000000.47</v>
+        <v>4396.12</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>147059573.11</v>
+        <v>161622.89</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>9490250.18</v>
+        <v>10430.07</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>16624999.6</v>
+        <v>18271.37</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>31333773.44</v>
+        <v>34436.76</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>440000</v>
+        <v>483.57</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>20715035.55</v>
+        <v>22766.45</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>18639000.05</v>
+        <v>20484.82</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>27060000.72</v>
+        <v>29739.75</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2999999.64995372</v>
+        <v>3297.09</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4930024.58</v>
+        <v>5418.25</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>999999.6</v>
+        <v>1099.03</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>18016750.24</v>
+        <v>19800.95</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>46962300.6</v>
+        <v>51612.98</v>
       </c>
     </row>
     <row r="50">
@@ -3493,11 +3493,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>12200000.2599537</v>
+        <v>13408.17</v>
       </c>
     </row>
     <row r="51">
@@ -3558,11 +3558,11 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>148444591.26</v>
+        <v>163145.07</v>
       </c>
     </row>
     <row r="52">
@@ -3619,11 +3619,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7000000.48</v>
+        <v>7693.21</v>
       </c>
     </row>
     <row r="53">
@@ -3680,11 +3680,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>13258959.59</v>
+        <v>14572</v>
       </c>
     </row>
     <row r="54">
@@ -3741,11 +3741,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3540000.20004628</v>
+        <v>3890.57</v>
       </c>
     </row>
     <row r="55">
@@ -3802,11 +3802,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>29779338.2</v>
+        <v>32728.39</v>
       </c>
     </row>
     <row r="56">
@@ -3863,11 +3863,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1584000</v>
+        <v>1740.86</v>
       </c>
     </row>
     <row r="57">
@@ -3924,11 +3924,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>11979499.26</v>
+        <v>13165.83</v>
       </c>
     </row>
     <row r="58">
@@ -3985,11 +3985,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2999149.8</v>
+        <v>3296.16</v>
       </c>
     </row>
     <row r="59">
@@ -4046,11 +4046,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>62730540.6</v>
+        <v>68942.75</v>
       </c>
     </row>
     <row r="60">
@@ -4107,11 +4107,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>11305000</v>
+        <v>12424.54</v>
       </c>
     </row>
     <row r="61">
@@ -4168,11 +4168,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6336000</v>
+        <v>6963.45</v>
       </c>
     </row>
     <row r="62">
@@ -4229,11 +4229,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>404999.36</v>
+        <v>445.11</v>
       </c>
     </row>
     <row r="63">
@@ -4294,11 +4294,11 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>62568000</v>
+        <v>68764.11</v>
       </c>
     </row>
     <row r="64">
@@ -4355,11 +4355,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3686949.39</v>
+        <v>4052.07</v>
       </c>
     </row>
     <row r="65">
@@ -4416,11 +4416,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4337700.24</v>
+        <v>4767.26</v>
       </c>
     </row>
     <row r="66">
@@ -4477,11 +4477,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>37566230.11</v>
+        <v>41286.42</v>
       </c>
     </row>
     <row r="67">
@@ -4538,11 +4538,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>399999.16</v>
+        <v>439.61</v>
       </c>
     </row>
     <row r="68">
@@ -4599,11 +4599,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>11000000.14</v>
+        <v>12089.33</v>
       </c>
     </row>
     <row r="69">
@@ -4660,11 +4660,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2640000</v>
+        <v>2901.44</v>
       </c>
     </row>
     <row r="70">
@@ -4721,11 +4721,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3552120</v>
+        <v>3903.89</v>
       </c>
     </row>
     <row r="71">
@@ -4782,11 +4782,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5179352.97</v>
+        <v>5692.26</v>
       </c>
     </row>
     <row r="72">
@@ -4843,11 +4843,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>12698400</v>
+        <v>13955.92</v>
       </c>
     </row>
     <row r="73">
@@ -4908,11 +4908,11 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>219171923.53</v>
+        <v>240876.54</v>
       </c>
     </row>
     <row r="74">
@@ -4969,11 +4969,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2000000.33</v>
+        <v>2198.06</v>
       </c>
     </row>
     <row r="75">
@@ -5030,11 +5030,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>150000000.22</v>
+        <v>164854.51</v>
       </c>
     </row>
     <row r="76">
@@ -5091,11 +5091,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>171999.92</v>
+        <v>189.03</v>
       </c>
     </row>
     <row r="77">
@@ -5152,11 +5152,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1775549.73</v>
+        <v>1951.38</v>
       </c>
     </row>
     <row r="78">
@@ -5213,11 +5213,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>15247500.05</v>
+        <v>16757.46</v>
       </c>
     </row>
     <row r="79">
@@ -5274,11 +5274,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>55000000.72</v>
+        <v>60446.66</v>
       </c>
     </row>
     <row r="80">
@@ -5335,11 +5335,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>23394890.32</v>
+        <v>25711.69</v>
       </c>
     </row>
     <row r="81">
@@ -5396,11 +5396,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1896959.78</v>
+        <v>2084.82</v>
       </c>
     </row>
     <row r="82">
@@ -5457,11 +5457,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>11274599.72</v>
+        <v>12391.12</v>
       </c>
     </row>
     <row r="83">
@@ -5518,11 +5518,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>14616129.36</v>
+        <v>16063.57</v>
       </c>
     </row>
     <row r="84">
@@ -5579,11 +5579,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1699357.44</v>
+        <v>1867.64</v>
       </c>
     </row>
     <row r="85">
@@ -5640,11 +5640,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10463908</v>
+        <v>11500.15</v>
       </c>
     </row>
     <row r="86">
@@ -5701,11 +5701,11 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>19536274.51</v>
+        <v>21470.95</v>
       </c>
     </row>
     <row r="87">
@@ -5762,11 +5762,11 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>19950000.2</v>
+        <v>21925.65</v>
       </c>
     </row>
     <row r="88">
@@ -5823,11 +5823,11 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>18497832.32</v>
+        <v>20329.67</v>
       </c>
     </row>
     <row r="89">
@@ -5884,11 +5884,11 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>7937249.54</v>
+        <v>8723.280000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5945,11 +5945,11 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>10488000.09</v>
+        <v>11526.63</v>
       </c>
     </row>
     <row r="91">
@@ -6006,11 +6006,11 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>41413349.88</v>
+        <v>45514.52</v>
       </c>
     </row>
     <row r="92">
@@ -6067,11 +6067,11 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>24882399.96</v>
+        <v>27346.51</v>
       </c>
     </row>
     <row r="93">
@@ -6128,11 +6128,11 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>26518300.16</v>
+        <v>29144.41</v>
       </c>
     </row>
     <row r="94">
@@ -6189,11 +6189,11 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2099903.75</v>
+        <v>2307.86</v>
       </c>
     </row>
     <row r="95">
@@ -6250,11 +6250,11 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>309225.67</v>
+        <v>339.85</v>
       </c>
     </row>
     <row r="96">
@@ -6311,11 +6311,11 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>22585965.57</v>
+        <v>24822.66</v>
       </c>
     </row>
     <row r="97">
@@ -6372,11 +6372,11 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>12636996.93</v>
+        <v>13888.44</v>
       </c>
     </row>
     <row r="98">
@@ -6433,11 +6433,11 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>22610000</v>
+        <v>24849.07</v>
       </c>
     </row>
     <row r="99">
@@ -6494,11 +6494,11 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6489070</v>
+        <v>7131.68</v>
       </c>
     </row>
     <row r="100">
@@ -6555,11 +6555,11 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2000000.33</v>
+        <v>2198.06</v>
       </c>
     </row>
     <row r="101">
@@ -6616,11 +6616,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1999999.2</v>
+        <v>2198.06</v>
       </c>
     </row>
     <row r="102">
@@ -6677,11 +6677,11 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>10156450.44</v>
+        <v>11162.24</v>
       </c>
     </row>
     <row r="103">
@@ -6738,11 +6738,11 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>11545295.69</v>
+        <v>12688.63</v>
       </c>
     </row>
     <row r="104">
@@ -6799,11 +6799,11 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>271679.5</v>
+        <v>298.58</v>
       </c>
     </row>
     <row r="105">
@@ -6860,11 +6860,11 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>20160899.5</v>
+        <v>22157.44</v>
       </c>
     </row>
     <row r="106">
@@ -6921,11 +6921,11 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>12824999.08</v>
+        <v>14095.06</v>
       </c>
     </row>
     <row r="107">
@@ -6982,11 +6982,11 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2000000.33</v>
+        <v>2198.06</v>
       </c>
     </row>
     <row r="108">
@@ -7043,11 +7043,11 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>140999.35</v>
+        <v>154.96</v>
       </c>
     </row>
     <row r="109">
@@ -7104,11 +7104,11 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2277764.72</v>
+        <v>2503.33</v>
       </c>
     </row>
     <row r="110">
@@ -7165,11 +7165,11 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3510202.5</v>
+        <v>3857.82</v>
       </c>
     </row>
     <row r="111">
@@ -7226,11 +7226,11 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1256849.2</v>
+        <v>1381.32</v>
       </c>
     </row>
     <row r="112">
@@ -7287,11 +7287,11 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>319999.33</v>
+        <v>351.69</v>
       </c>
     </row>
     <row r="113">
@@ -7348,11 +7348,11 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>359999.81</v>
+        <v>395.65</v>
       </c>
     </row>
     <row r="114">
@@ -7409,11 +7409,11 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>152617.5</v>
+        <v>167.73</v>
       </c>
     </row>
     <row r="115">
@@ -7470,11 +7470,11 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>541500.46</v>
+        <v>595.13</v>
       </c>
     </row>
     <row r="116">
@@ -7531,11 +7531,11 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>376199.88</v>
+        <v>413.45</v>
       </c>
     </row>
     <row r="117">
@@ -7592,11 +7592,11 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1551999.01</v>
+        <v>1705.69</v>
       </c>
     </row>
     <row r="118">
@@ -7653,11 +7653,11 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>956079.6800000001</v>
+        <v>1050.76</v>
       </c>
     </row>
     <row r="119">
@@ -7714,11 +7714,11 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>10761600.3</v>
+        <v>11827.32</v>
       </c>
     </row>
     <row r="120">
@@ -7775,11 +7775,11 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>4522000</v>
+        <v>4969.81</v>
       </c>
     </row>
     <row r="121">
@@ -7836,11 +7836,11 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>78207360</v>
+        <v>85952.24000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7897,11 +7897,11 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>8698200.4</v>
+        <v>9559.58</v>
       </c>
     </row>
     <row r="123">
@@ -7958,11 +7958,11 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>23999994.97</v>
+        <v>26376.72</v>
       </c>
     </row>
     <row r="124">
@@ -8019,11 +8019,11 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>11656735.86</v>
+        <v>12811.1</v>
       </c>
     </row>
     <row r="125">
@@ -8084,11 +8084,11 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>189072000.46</v>
+        <v>207795.82</v>
       </c>
     </row>
     <row r="126">
@@ -8145,11 +8145,11 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>30979024.8</v>
+        <v>34046.88</v>
       </c>
     </row>
     <row r="127">
@@ -8206,11 +8206,11 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>6726000.19</v>
+        <v>7392.08</v>
       </c>
     </row>
     <row r="128">
@@ -8267,11 +8267,11 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2097181.51</v>
+        <v>2304.87</v>
       </c>
     </row>
     <row r="129">
@@ -8328,11 +8328,11 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1259225.51</v>
+        <v>1383.93</v>
       </c>
     </row>
     <row r="130">
@@ -8389,11 +8389,11 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1855663.92</v>
+        <v>2039.43</v>
       </c>
     </row>
     <row r="131">
@@ -8450,11 +8450,11 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>495503.8</v>
+        <v>544.5700000000001</v>
       </c>
     </row>
     <row r="132">
@@ -8511,11 +8511,11 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>307800.1</v>
+        <v>338.28</v>
       </c>
     </row>
     <row r="133">
@@ -8572,11 +8572,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>24107199.15</v>
+        <v>26494.54</v>
       </c>
     </row>
     <row r="134">
@@ -8633,11 +8633,11 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1031016</v>
+        <v>1133.12</v>
       </c>
     </row>
     <row r="135">
@@ -8694,11 +8694,11 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>9074400.279999999</v>
+        <v>9973.040000000001</v>
       </c>
     </row>
     <row r="136">
@@ -8755,11 +8755,11 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>37100349.93</v>
+        <v>40774.4</v>
       </c>
     </row>
     <row r="137">
@@ -8816,11 +8816,11 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>7497875.07</v>
+        <v>8240.389999999999</v>
       </c>
     </row>
     <row r="138">
@@ -8877,11 +8877,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>788974.8199999999</v>
+        <v>867.11</v>
       </c>
     </row>
     <row r="139">
@@ -8938,17 +8938,17 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2210174.98</v>
+        <v>2429.05</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1738-95-CM26</t>
+          <t>1953-418-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8968,22 +8968,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.130.200-8</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
+          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8999,11 +8999,11 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>21560000</v>
+        <v>5495.15</v>
       </c>
     </row>
     <row r="141">
@@ -9060,11 +9060,11 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>7461300</v>
+        <v>8200.190000000001</v>
       </c>
     </row>
     <row r="142">
@@ -9121,11 +9121,11 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3280024</v>
+        <v>3604.85</v>
       </c>
     </row>
     <row r="143">
@@ -9182,11 +9182,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>3942400</v>
+        <v>4332.82</v>
       </c>
     </row>
     <row r="144">
@@ -9243,11 +9243,11 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2495000.04</v>
+        <v>2742.08</v>
       </c>
     </row>
     <row r="145">
@@ -9304,17 +9304,17 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>16340000.55</v>
+        <v>17958.15</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1953-418-CM26</t>
+          <t>1738-95-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9334,22 +9334,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>69.130.200-8</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9365,11 +9365,11 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>5000000.35002314</v>
+        <v>23695.09</v>
       </c>
     </row>
     <row r="147">
@@ -9426,11 +9426,11 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>660000</v>
+        <v>725.36</v>
       </c>
     </row>
     <row r="148">
@@ -9487,11 +9487,11 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>24576500.23</v>
+        <v>27010.31</v>
       </c>
     </row>
     <row r="149">
@@ -9548,11 +9548,11 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>13530000.36</v>
+        <v>14869.88</v>
       </c>
     </row>
     <row r="150">
@@ -9609,17 +9609,17 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>41243774.88</v>
+        <v>45328.15</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2755-62-CM26</t>
+          <t>2436-296-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9644,17 +9644,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9670,17 +9670,17 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>495000.73</v>
+        <v>33907.77</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2436-296-CM26</t>
+          <t>2755-62-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9705,17 +9705,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9731,11 +9731,11 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>30852449.76</v>
+        <v>544.02</v>
       </c>
     </row>
     <row r="153">
@@ -9792,11 +9792,11 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>16368000</v>
+        <v>17988.92</v>
       </c>
     </row>
     <row r="154">
@@ -9853,11 +9853,11 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>237600</v>
+        <v>261.13</v>
       </c>
     </row>
     <row r="155">
@@ -9914,11 +9914,11 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>8369499.61</v>
+        <v>9198.33</v>
       </c>
     </row>
     <row r="156">
@@ -9975,11 +9975,11 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>20115870.55</v>
+        <v>22107.95</v>
       </c>
     </row>
     <row r="157">
@@ -10036,11 +10036,11 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>8062828.4</v>
+        <v>8861.290000000001</v>
       </c>
     </row>
     <row r="158">
@@ -10097,11 +10097,11 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>5032150.56</v>
+        <v>5530.48</v>
       </c>
     </row>
     <row r="159">
@@ -10158,11 +10158,11 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>19120649.57</v>
+        <v>21014.17</v>
       </c>
     </row>
     <row r="160">
@@ -10219,11 +10219,11 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1499992.62</v>
+        <v>1648.54</v>
       </c>
     </row>
     <row r="161">
@@ -10280,11 +10280,11 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1144000</v>
+        <v>1257.29</v>
       </c>
     </row>
     <row r="162">
@@ -10341,11 +10341,11 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1240000.23</v>
+        <v>1362.8</v>
       </c>
     </row>
     <row r="163">
@@ -10402,11 +10402,11 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3116999.81004628</v>
+        <v>3425.68</v>
       </c>
     </row>
     <row r="164">
@@ -10463,11 +10463,11 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>5820795.2</v>
+        <v>6397.23</v>
       </c>
     </row>
     <row r="165">
@@ -10524,11 +10524,11 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>999226.34</v>
+        <v>1098.18</v>
       </c>
     </row>
     <row r="166">
@@ -10585,11 +10585,11 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>228800</v>
+        <v>251.46</v>
       </c>
     </row>
     <row r="167">
@@ -10646,11 +10646,11 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2640000</v>
+        <v>2901.44</v>
       </c>
     </row>
     <row r="168">
@@ -10707,11 +10707,11 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1526175</v>
+        <v>1677.31</v>
       </c>
     </row>
     <row r="169">
@@ -10768,11 +10768,11 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>660000</v>
+        <v>725.36</v>
       </c>
     </row>
     <row r="170">
@@ -10829,11 +10829,11 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1106850</v>
+        <v>1216.46</v>
       </c>
     </row>
     <row r="171">
@@ -10890,11 +10890,11 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>10407196.47</v>
+        <v>11437.82</v>
       </c>
     </row>
     <row r="172">
@@ -10951,11 +10951,11 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1416469.12</v>
+        <v>1556.74</v>
       </c>
     </row>
     <row r="173">
@@ -11012,11 +11012,11 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>33359216</v>
+        <v>36662.78</v>
       </c>
     </row>
     <row r="174">
@@ -11077,11 +11077,11 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>231418855.9311</v>
+        <v>254336.28</v>
       </c>
     </row>
     <row r="175">
@@ -11138,11 +11138,11 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>585200</v>
+        <v>643.15</v>
       </c>
     </row>
     <row r="176">
@@ -11203,11 +11203,11 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>110000000.25</v>
+        <v>120893.31</v>
       </c>
     </row>
     <row r="177">
@@ -11264,11 +11264,11 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1200000.88</v>
+        <v>1318.84</v>
       </c>
     </row>
     <row r="178">
@@ -11325,11 +11325,11 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>15000000.81</v>
+        <v>16485.45</v>
       </c>
     </row>
     <row r="179">
@@ -11386,11 +11386,11 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1829520</v>
+        <v>2010.7</v>
       </c>
     </row>
     <row r="180">
@@ -11447,11 +11447,11 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1992885.84</v>
+        <v>2190.24</v>
       </c>
     </row>
     <row r="181">
@@ -11508,11 +11508,11 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1250000.08997686</v>
+        <v>1373.79</v>
       </c>
     </row>
     <row r="182">
@@ -11569,11 +11569,11 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>25564000</v>
+        <v>28095.61</v>
       </c>
     </row>
     <row r="183">
@@ -11630,11 +11630,11 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>9644800</v>
+        <v>10599.93</v>
       </c>
     </row>
     <row r="184">
@@ -11691,11 +11691,11 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3539260.87</v>
+        <v>3889.75</v>
       </c>
     </row>
     <row r="185">
@@ -11752,11 +11752,11 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>32832100.83</v>
+        <v>36083.47</v>
       </c>
     </row>
     <row r="186">
@@ -11813,11 +11813,11 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>9708999.67</v>
+        <v>10670.48</v>
       </c>
     </row>
     <row r="187">
@@ -11874,11 +11874,11 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>664000.3100000001</v>
+        <v>729.76</v>
       </c>
     </row>
     <row r="188">
@@ -11935,11 +11935,11 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>11063129.53</v>
+        <v>12158.71</v>
       </c>
     </row>
     <row r="189">
@@ -12000,11 +12000,11 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>295999412.9984</v>
+        <v>325312.26</v>
       </c>
     </row>
     <row r="190">
@@ -12061,11 +12061,11 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>26828570.41</v>
+        <v>29485.41</v>
       </c>
     </row>
     <row r="191">
@@ -12122,11 +12122,11 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1500000.29004628</v>
+        <v>1648.55</v>
       </c>
     </row>
     <row r="192">
@@ -12183,11 +12183,11 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>50832800.23</v>
+        <v>55866.78</v>
       </c>
     </row>
     <row r="193">
@@ -12244,11 +12244,11 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1699999.55</v>
+        <v>1868.35</v>
       </c>
     </row>
     <row r="194">
@@ -12305,11 +12305,11 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3191999.53</v>
+        <v>3508.1</v>
       </c>
     </row>
     <row r="195">
@@ -12366,11 +12366,11 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1056000</v>
+        <v>1160.58</v>
       </c>
     </row>
     <row r="196">
@@ -12427,11 +12427,11 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>31840199</v>
+        <v>34993.34</v>
       </c>
     </row>
     <row r="197">
@@ -12488,11 +12488,11 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>5878600</v>
+        <v>6460.76</v>
       </c>
     </row>
     <row r="198">
@@ -12549,11 +12549,11 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>14333255.65</v>
+        <v>15752.68</v>
       </c>
     </row>
     <row r="199">
@@ -12610,11 +12610,11 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>16000000.42</v>
+        <v>17584.48</v>
       </c>
     </row>
     <row r="200">
@@ -12671,11 +12671,11 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2816000</v>
+        <v>3094.87</v>
       </c>
     </row>
     <row r="201">
@@ -12732,11 +12732,11 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>14678400</v>
+        <v>16132</v>
       </c>
     </row>
     <row r="202">
@@ -12797,11 +12797,11 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>72302086.9610042</v>
+        <v>79462.17</v>
       </c>
     </row>
     <row r="203">
@@ -12858,11 +12858,11 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>3829301.95</v>
+        <v>4208.52</v>
       </c>
     </row>
     <row r="204">
@@ -12919,11 +12919,11 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>46632960</v>
+        <v>51251.03</v>
       </c>
     </row>
     <row r="205">
@@ -12980,11 +12980,11 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>13119975.92</v>
+        <v>14419.25</v>
       </c>
     </row>
     <row r="206">
@@ -13041,11 +13041,11 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>9791526.800000001</v>
+        <v>10761.18</v>
       </c>
     </row>
     <row r="207">
@@ -13102,11 +13102,11 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>42000108.77</v>
+        <v>46159.38</v>
       </c>
     </row>
     <row r="208">
@@ -13163,11 +13163,11 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>14637599.82</v>
+        <v>16087.16</v>
       </c>
     </row>
     <row r="209">
@@ -13224,11 +13224,11 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>46363325.52</v>
+        <v>50954.69</v>
       </c>
     </row>
     <row r="210">
@@ -13285,11 +13285,11 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3295842</v>
+        <v>3622.23</v>
       </c>
     </row>
     <row r="211">
@@ -13346,11 +13346,11 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>11000000.14</v>
+        <v>12089.33</v>
       </c>
     </row>
     <row r="212">
@@ -13407,11 +13407,11 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>799999.46</v>
+        <v>879.22</v>
       </c>
     </row>
     <row r="213">
@@ -13468,11 +13468,11 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1496999.06</v>
+        <v>1645.25</v>
       </c>
     </row>
     <row r="214">
@@ -13529,11 +13529,11 @@
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3999999.54</v>
+        <v>4396.12</v>
       </c>
     </row>
     <row r="215">
@@ -13590,11 +13590,11 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>5697720</v>
+        <v>6261.97</v>
       </c>
     </row>
     <row r="216">
@@ -13651,11 +13651,11 @@
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2299999.99</v>
+        <v>2527.77</v>
       </c>
     </row>
     <row r="217">
@@ -13712,11 +13712,11 @@
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>5350400</v>
+        <v>5880.25</v>
       </c>
     </row>
     <row r="218">
@@ -13773,11 +13773,11 @@
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>6999998.34</v>
+        <v>7693.21</v>
       </c>
     </row>
     <row r="219">
@@ -13834,11 +13834,11 @@
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1208400.49</v>
+        <v>1328.07</v>
       </c>
     </row>
     <row r="220">
@@ -13895,11 +13895,11 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>53000000.24</v>
+        <v>58248.59</v>
       </c>
     </row>
     <row r="221">
@@ -13956,11 +13956,11 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>6806250</v>
+        <v>7480.27</v>
       </c>
     </row>
     <row r="222">
@@ -14017,11 +14017,11 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1250000.4</v>
+        <v>1373.79</v>
       </c>
     </row>
     <row r="223">
@@ -14078,11 +14078,11 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>336300.01</v>
+        <v>369.6</v>
       </c>
     </row>
     <row r="224">
@@ -14139,11 +14139,11 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>11158699.73</v>
+        <v>12263.75</v>
       </c>
     </row>
     <row r="225">
@@ -14200,11 +14200,11 @@
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>900000.09</v>
+        <v>989.13</v>
       </c>
     </row>
     <row r="226">
@@ -14261,11 +14261,11 @@
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>6005899.95</v>
+        <v>6600.66</v>
       </c>
     </row>
     <row r="227">
@@ -14322,11 +14322,11 @@
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>35000000.77</v>
+        <v>38466.05</v>
       </c>
     </row>
     <row r="228">
@@ -14383,11 +14383,11 @@
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>30400.28</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="229">
@@ -14444,11 +14444,11 @@
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>600000.4399999999</v>
+        <v>659.42</v>
       </c>
     </row>
     <row r="230">
@@ -14505,17 +14505,17 @@
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>22799.92</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3970-3-CM26</t>
+          <t>1079639-159-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14540,17 +14540,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14566,17 +14566,17 @@
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>27550000.11</v>
+        <v>42906.41</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1079639-159-CM26</t>
+          <t>1079639-160-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14627,17 +14627,17 @@
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>39040249.5</v>
+        <v>37421.86</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1079639-160-CM26</t>
+          <t>1057374-183-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14662,17 +14662,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.042-0</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14688,17 +14688,17 @@
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>34049900.3</v>
+        <v>15452.89</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1057374-183-CM26</t>
+          <t>3970-3-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14723,17 +14723,17 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.602.042-0</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
+          <t>Dirección General de Carabineros de Chile</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14749,17 +14749,17 @@
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>14060480.7</v>
+        <v>30278.28</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1079969-56-CM26</t>
+          <t>1051765-220-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14784,17 +14784,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>Dirección Regional de Ñuble</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14810,17 +14810,17 @@
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>45599.85</v>
+        <v>164.85</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1051765-220-CM26</t>
+          <t>1628-79-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14845,17 +14845,17 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14871,17 +14871,17 @@
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>149999.26</v>
+        <v>13188.36</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1628-79-CM26</t>
+          <t>1301883-64-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14901,22 +14901,22 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14932,17 +14932,17 @@
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>12000000.88</v>
+        <v>338.5</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1301883-64-CM26</t>
+          <t>1620-78-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14962,22 +14962,22 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -14993,17 +14993,17 @@
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>308000</v>
+        <v>10995.71</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1620-78-CM26</t>
+          <t>1079969-56-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15028,17 +15028,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15054,17 +15054,17 @@
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>10004925</v>
+        <v>50.12</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1529-88-CM26</t>
+          <t>1193180-16-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15089,12 +15089,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>60.511.060-6</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15115,17 +15115,17 @@
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>45658387.55</v>
+        <v>1044.52</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1077908-58-CM26</t>
+          <t>1529-88-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15150,17 +15150,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15176,17 +15176,17 @@
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>33094806.42</v>
+        <v>50179.94</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1070329-81-CM26</t>
+          <t>1077908-58-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15211,17 +15211,17 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15237,17 +15237,17 @@
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>13500972.51</v>
+        <v>36372.19</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1557-93-CM26</t>
+          <t>1070329-81-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15272,17 +15272,17 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15298,17 +15298,17 @@
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>17102612.11</v>
+        <v>14837.97</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1079659-102-CM26</t>
+          <t>1557-93-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15333,17 +15333,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15359,17 +15359,17 @@
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3868400.29</v>
+        <v>18796.29</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1193180-16-CM26</t>
+          <t>1383-88-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15389,22 +15389,22 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>60.511.060-6</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15420,17 +15420,17 @@
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>950400</v>
+        <v>8541.610000000001</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1702-197-CM26</t>
+          <t>1079659-102-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.606.605-6</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15481,17 +15481,17 @@
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>30000000.5</v>
+        <v>4251.49</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1383-88-CM26</t>
+          <t>1057506-3852-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15511,22 +15511,22 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15542,17 +15542,17 @@
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>7771948.96</v>
+        <v>18015.58</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1057506-3852-CM26</t>
+          <t>2045-110-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15577,17 +15577,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15603,11 +15603,11 @@
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>16392250</v>
+        <v>8242.73</v>
       </c>
     </row>
     <row r="249">
@@ -15664,11 +15664,11 @@
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>21000168</v>
+        <v>23079.82</v>
       </c>
     </row>
     <row r="250">
@@ -15725,11 +15725,11 @@
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>912000.35</v>
+        <v>1002.32</v>
       </c>
     </row>
     <row r="251">
@@ -15786,11 +15786,11 @@
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>899878</v>
+        <v>988.99</v>
       </c>
     </row>
     <row r="252">
@@ -15847,11 +15847,11 @@
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2000000.33</v>
+        <v>2198.06</v>
       </c>
     </row>
     <row r="253">
@@ -15908,11 +15908,11 @@
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>36000000.37</v>
+        <v>39565.08</v>
       </c>
     </row>
     <row r="254">
@@ -15969,17 +15969,17 @@
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>9060150.32</v>
+        <v>9957.379999999999</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2045-110-CM26</t>
+          <t>1702-197-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16004,17 +16004,17 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>61.606.605-6</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16030,11 +16030,11 @@
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>7500000.41</v>
+        <v>32970.9</v>
       </c>
     </row>
     <row r="256">
@@ -16091,11 +16091,11 @@
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>408975.33</v>
+        <v>449.48</v>
       </c>
     </row>
     <row r="257">
@@ -16152,11 +16152,11 @@
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3264650.4</v>
+        <v>3587.95</v>
       </c>
     </row>
     <row r="258">
@@ -16213,11 +16213,11 @@
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>306000.35</v>
+        <v>336.3</v>
       </c>
     </row>
     <row r="259">
@@ -16274,17 +16274,17 @@
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>17099999.53</v>
+        <v>18793.41</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>585-47-CM26</t>
+          <t>509876-20-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16304,22 +16304,22 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16335,11 +16335,11 @@
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>25654088.31</v>
+        <v>5283.22</v>
       </c>
     </row>
     <row r="261">
@@ -16396,11 +16396,11 @@
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>440000</v>
+        <v>483.57</v>
       </c>
     </row>
     <row r="262">
@@ -16457,11 +16457,11 @@
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>341999.99</v>
+        <v>375.87</v>
       </c>
     </row>
     <row r="263">
@@ -16518,11 +16518,11 @@
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>50516406.07</v>
+        <v>55519.05</v>
       </c>
     </row>
     <row r="264">
@@ -16579,11 +16579,11 @@
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>11400000.44</v>
+        <v>12528.94</v>
       </c>
     </row>
     <row r="265">
@@ -16640,17 +16640,17 @@
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>805599.95</v>
+        <v>885.38</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>509876-20-CM26</t>
+          <t>585-47-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16670,22 +16670,22 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16701,17 +16701,17 @@
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>4807168.96</v>
+        <v>28194.61</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1624-66-CM26</t>
+          <t>1057496-646-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16736,17 +16736,17 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.608.105-5</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL SAN LUIS</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16762,17 +16762,17 @@
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>9326625</v>
+        <v>5088.32</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1057496-646-CM26</t>
+          <t>1624-66-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16797,17 +16797,17 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.608.105-5</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL SAN LUIS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16823,11 +16823,11 @@
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>4629824.83</v>
+        <v>10250.24</v>
       </c>
     </row>
     <row r="269">
@@ -16884,11 +16884,11 @@
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>4245074.98</v>
+        <v>4665.47</v>
       </c>
     </row>
     <row r="270">
@@ -16945,11 +16945,11 @@
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>332500.4</v>
+        <v>365.43</v>
       </c>
     </row>
     <row r="271">
@@ -17006,11 +17006,11 @@
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>3324999.47</v>
+        <v>3654.27</v>
       </c>
     </row>
     <row r="272">
@@ -17067,11 +17067,11 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>14447125.27</v>
+        <v>15877.83</v>
       </c>
     </row>
     <row r="273">
@@ -17128,11 +17128,11 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>34661797</v>
+        <v>38094.36</v>
       </c>
     </row>
     <row r="274">
@@ -17189,11 +17189,11 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>11584976.48</v>
+        <v>12732.24</v>
       </c>
     </row>
     <row r="275">
@@ -17250,11 +17250,11 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>26454460.83</v>
+        <v>29074.25</v>
       </c>
     </row>
     <row r="276">
@@ -17311,11 +17311,11 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5700000.22</v>
+        <v>6264.47</v>
       </c>
     </row>
     <row r="277">
@@ -17376,11 +17376,11 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>331278299.94</v>
+        <v>364084.82</v>
       </c>
     </row>
     <row r="278">
@@ -17437,17 +17437,17 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>702385.2</v>
+        <v>771.9400000000001</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4291-261-CM26</t>
+          <t>1057541-276-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17467,22 +17467,22 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17498,17 +17498,17 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>7500867.5</v>
+        <v>2088.16</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1057541-276-CM26</t>
+          <t>1467-10-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17528,22 +17528,22 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>60.511.071-1</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CURICÓ</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17559,17 +17559,17 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1899999.7</v>
+        <v>1099.03</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1467-10-CM26</t>
+          <t>1464-467-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17589,17 +17589,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>60.511.071-1</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CURICÓ</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17620,17 +17620,17 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1000000.32</v>
+        <v>31061.34</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1464-467-CM26</t>
+          <t>1099899-62-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17655,17 +17655,17 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17681,17 +17681,17 @@
       <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>28262500</v>
+        <v>28685.01</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1099899-62-CM26</t>
+          <t>1373324-28-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17716,17 +17716,17 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17742,17 +17742,17 @@
       <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>26100300.05</v>
+        <v>2740.83</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1373324-28-CM26</t>
+          <t>1373324-29-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17803,17 +17803,17 @@
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2493865.44</v>
+        <v>640.87</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1373324-29-CM26</t>
+          <t>3495-66-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17838,17 +17838,17 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17864,17 +17864,17 @@
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>583123.2</v>
+        <v>17232.79</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3495-66-CM26</t>
+          <t>4291-261-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17894,22 +17894,22 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17925,17 +17925,17 @@
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>15680000.16</v>
+        <v>8243.68</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2102-242-CM26</t>
+          <t>2085-244-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17986,17 +17986,17 @@
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>37756799.63</v>
+        <v>28459.91</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2085-244-CM26</t>
+          <t>2102-242-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18021,17 +18021,17 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18047,17 +18047,17 @@
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>25895480.58</v>
+        <v>41495.86</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1057681-30-CM26</t>
+          <t>707427-17-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18082,17 +18082,17 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.608.401-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Dirección Servicio Metropolitano Oriente</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18108,17 +18108,17 @@
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2000000.70995372</v>
+        <v>3512.47</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>707427-17-CM26</t>
+          <t>1075337-7538-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18138,22 +18138,22 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18169,11 +18169,11 @@
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>3195968.16</v>
+        <v>30988.46</v>
       </c>
     </row>
     <row r="291">
@@ -18230,11 +18230,11 @@
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1020000.08</v>
+        <v>1121.01</v>
       </c>
     </row>
     <row r="292">
@@ -18291,11 +18291,11 @@
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>4007048.32</v>
+        <v>4403.87</v>
       </c>
     </row>
     <row r="293">
@@ -18352,11 +18352,11 @@
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2196788</v>
+        <v>2414.34</v>
       </c>
     </row>
     <row r="294">
@@ -18413,17 +18413,17 @@
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>9160782.91</v>
+        <v>10067.98</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1009566-43-CM26</t>
+          <t>5701-21-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18443,17 +18443,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.999.360-8</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. de la División Logística</t>
+          <t>Dirección General de Carabineros de Chile</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18474,17 +18474,17 @@
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>320770.780023142</v>
+        <v>3290.41</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5701-21-CM26</t>
+          <t>3481-37-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18509,17 +18509,17 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>REGIMIENTO 12 "SANGRA"</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18535,17 +18535,17 @@
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2993924.63</v>
+        <v>1648.55</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3481-37-CM26</t>
+          <t>3374-30-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18570,17 +18570,17 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18596,17 +18596,17 @@
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1500000.53</v>
+        <v>5495.15</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3374-30-CM26</t>
+          <t>3365-36-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18631,7 +18631,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18657,17 +18657,17 @@
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>5000000.27</v>
+        <v>2747.58</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3365-36-CM26</t>
+          <t>1099899-63-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18692,17 +18692,17 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18718,17 +18718,17 @@
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2500000.14</v>
+        <v>5534.66</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1099899-63-CM26</t>
+          <t>1057681-30-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18748,22 +18748,22 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.608.401-1</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>Dirección Servicio Metropolitano Oriente</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18779,17 +18779,17 @@
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>5035950.17</v>
+        <v>2198.06</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1075337-7538-CM26</t>
+          <t>517903-28-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18814,17 +18814,17 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.114.000-2</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>EMDN-RMA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18837,79 +18837,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>28196190.52</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>517903-28-CM26</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2239-13-LR23</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>mar-2026</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>61.114.000-2</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>EMDN-RMA</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>Magallanes y Antártica</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M302" s="2" t="n">
-        <v>109250000.37</v>
+        <v>120069.04</v>
       </c>
     </row>
   </sheetData>
